--- a/author.xlsx
+++ b/author.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E423E463-E0CF-4DB2-B8E8-BBFD2AD0CC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A02844-8142-46B4-88F1-ACABB30F9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
   <si>
     <t>Short Description</t>
   </si>
@@ -221,6 +221,33 @@
   </si>
   <si>
     <t xml:space="preserve">Efficient license plate recognition using a Jetson Nano for real-time car license plate identification	</t>
+  </si>
+  <si>
+    <t>Mansour</t>
+  </si>
+  <si>
+    <t>Ahmady Phoulady</t>
+  </si>
+  <si>
+    <t>MansourAP</t>
+  </si>
+  <si>
+    <t>mansour.ahmady.phoulady@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>sherwin.ap@gmail.com</t>
+  </si>
+  <si>
+    <t>&lt;09.07.1985&gt;</t>
+  </si>
+  <si>
+    <t>&lt;26725 Emden&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Martin-Faber-Str.&gt;</t>
+  </si>
+  <si>
+    <t>&lt;0157 333 47 662&gt;</t>
   </si>
 </sst>
 </file>
@@ -611,14 +638,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" customWidth="1"/>
+    <col min="1" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:14" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
       <c r="B1" s="6"/>
       <c r="C1" s="11" t="s">
@@ -636,24 +663,24 @@
       <c r="M1" s="11"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -674,22 +701,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43" customWidth="1"/>
-    <col min="6" max="6" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -709,7 +736,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -729,10 +756,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -740,7 +767,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -748,7 +775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -756,7 +783,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -764,12 +791,12 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -777,7 +804,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -785,12 +812,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -798,7 +825,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -806,7 +833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -814,17 +841,17 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -832,7 +859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -840,12 +867,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -853,25 +880,25 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
@@ -879,12 +906,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
@@ -892,21 +919,21 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
@@ -914,7 +941,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -922,7 +949,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -930,13 +957,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
@@ -964,20 +991,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -997,55 +1026,64 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>7025671</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45595</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1053,54 +1091,54 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1108,7 +1146,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1116,112 +1154,103 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
@@ -1236,6 +1265,11 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{0711D0FA-1011-4E6A-82F9-0EBE42089C5F}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{2E5B0E0D-625B-4F13-A906-28EB4032399E}"/>
+    <hyperlink ref="B40" r:id="rId3" xr:uid="{D27464EB-6073-44B0-94D8-B2B2953FC678}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1243,20 +1277,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1276,7 +1310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1287,15 +1321,15 @@
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1303,7 +1337,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -1311,7 +1345,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -1319,12 +1353,12 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1332,7 +1366,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,12 +1374,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1353,7 +1387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1361,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -1369,17 +1403,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -1387,7 +1421,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -1395,12 +1429,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
@@ -1408,7 +1442,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
@@ -1416,7 +1450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -1424,15 +1458,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
@@ -1440,7 +1474,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
@@ -1448,7 +1482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
@@ -1456,21 +1490,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
@@ -1478,7 +1512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -1486,7 +1520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -1494,13 +1528,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>23</v>
       </c>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11008"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A02844-8142-46B4-88F1-ACABB30F9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{32A02844-8142-46B4-88F1-ACABB30F9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42F5CFD-EB11-B34B-95DB-9CB66E653DD3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
   <si>
     <t>Short Description</t>
   </si>
@@ -37,18 +37,12 @@
     <t>Date of birth:</t>
   </si>
   <si>
-    <t>&lt;01.01.2000&gt;</t>
-  </si>
-  <si>
     <t>Address:</t>
   </si>
   <si>
     <t>Street home:</t>
   </si>
   <si>
-    <t>&lt;Steinweg 15&gt;</t>
-  </si>
-  <si>
     <t>City home:</t>
   </si>
   <si>
@@ -58,12 +52,6 @@
     <t>Company name/Department:</t>
   </si>
   <si>
-    <t>&lt;Hochschule Emden/Leer&gt; or &lt; VW Wolfsburg&gt; or &lt;...&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Fachbereich Technik&gt;  or &lt;Strak&gt; or &lt;...&gt;</t>
-  </si>
-  <si>
     <t>Street Workplace:</t>
   </si>
   <si>
@@ -76,24 +64,12 @@
     <t>Supervisor workplace:</t>
   </si>
   <si>
-    <t>&lt;Einstein, Albert&gt;</t>
-  </si>
-  <si>
-    <t>&lt;00494921 807-1001&gt;</t>
-  </si>
-  <si>
     <t>Email:</t>
   </si>
   <si>
-    <t>&lt;albert.einstein@hs-emden-leer.de&gt;</t>
-  </si>
-  <si>
     <t>Second examiner:</t>
   </si>
   <si>
-    <t>&lt;Prof. Dr. Carla Columna&gt;</t>
-  </si>
-  <si>
     <t>Outstanding examinations:</t>
   </si>
   <si>
@@ -145,15 +121,9 @@
     <t xml:space="preserve">Study: </t>
   </si>
   <si>
-    <t>&lt;04921 807 1429&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Workplace: </t>
   </si>
   <si>
-    <t>&lt;04921 807 1428&gt;</t>
-  </si>
-  <si>
     <t>Name, Surname</t>
   </si>
   <si>
@@ -248,6 +218,24 @@
   </si>
   <si>
     <t>&lt;0157 333 47 662&gt;</t>
+  </si>
+  <si>
+    <t>Hemanth-Jp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemanth.jadiswami.prabhakaran@stud.hs-emden-leer.de </t>
+  </si>
+  <si>
+    <t>hemanthjp139@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt;10&gt;</t>
+  </si>
+  <si>
+    <t>&lt;06.01.1996&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Graf-Johann-Straße 16 Port Arthur&gt;</t>
   </si>
 </sst>
 </file>
@@ -638,18 +626,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="5" width="11.5703125" customWidth="1"/>
+    <col min="1" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="7"/>
       <c r="B1" s="6"/>
       <c r="C1" s="11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -663,26 +651,26 @@
       <c r="M1" s="11"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -701,73 +689,73 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C5" s="8">
         <v>7026116</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -775,200 +763,200 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>45595</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1">
         <v>45688</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B40" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="B50" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -991,70 +979,70 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2">
         <v>7025671</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1062,200 +1050,200 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>45595</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1">
         <v>45688</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B40" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="B50" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1277,269 +1265,272 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7026000</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45595</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="B50" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{32A02844-8142-46B4-88F1-ACABB30F9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42F5CFD-EB11-B34B-95DB-9CB66E653DD3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70274BF2-B0BA-4BFB-877B-15BCC7179C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="12156" windowHeight="8964" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
     <sheet name="Ranjeetsing" sheetId="1" r:id="rId2"/>
-    <sheet name="Mansoor" sheetId="2" r:id="rId3"/>
+    <sheet name="Mansour" sheetId="2" r:id="rId3"/>
     <sheet name="Hemant" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -626,14 +626,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="5" width="11.5" customWidth="1"/>
+    <col min="1" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="5" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="7"/>
       <c r="B1" s="6"/>
       <c r="C1" s="11" t="s">
@@ -651,24 +651,24 @@
       <c r="M1" s="11"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -689,22 +689,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.1640625" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43" customWidth="1"/>
-    <col min="6" max="6" width="24.5" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -744,10 +744,10 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -755,7 +755,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -763,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -771,7 +771,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -779,12 +779,12 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -792,7 +792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -800,12 +800,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
@@ -813,7 +813,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -821,7 +821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -829,17 +829,17 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -847,7 +847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
@@ -855,12 +855,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>29</v>
       </c>
@@ -868,25 +868,25 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>33</v>
       </c>
@@ -894,12 +894,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
@@ -907,21 +907,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>33</v>
       </c>
@@ -929,7 +929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>11</v>
       </c>
@@ -937,7 +937,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>13</v>
       </c>
@@ -945,13 +945,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
@@ -979,22 +979,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1034,15 +1034,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1066,12 +1066,12 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,12 +1087,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -1116,17 +1116,17 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
@@ -1142,12 +1142,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>29</v>
       </c>
@@ -1155,25 +1155,25 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>33</v>
       </c>
@@ -1181,12 +1181,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
@@ -1194,21 +1194,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>33</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>11</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>13</v>
       </c>
@@ -1232,13 +1232,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
@@ -1265,20 +1265,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1318,10 +1318,10 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1353,12 +1353,12 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1374,12 +1374,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -1403,17 +1403,17 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
@@ -1429,12 +1429,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>29</v>
       </c>
@@ -1442,25 +1442,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>33</v>
       </c>
@@ -1468,12 +1468,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
@@ -1481,21 +1481,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>33</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>11</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>13</v>
       </c>
@@ -1519,13 +1519,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>15</v>
       </c>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0290E8CF-22B3-1D4A-9C9E-F24696FD0B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="25260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -12,20 +13,28 @@
     <sheet name="Student 2" sheetId="2" r:id="rId3"/>
     <sheet name="Student 3" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
-  <si>
-    <t>&lt;Project Name&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
   <si>
     <t>Short Description</t>
   </si>
@@ -159,9 +168,6 @@
     <t>Name, Surname</t>
   </si>
   <si>
-    <t>The nice project is…</t>
-  </si>
-  <si>
     <t>Name of the module:</t>
   </si>
   <si>
@@ -177,14 +183,53 @@
     <t>e-mail university</t>
   </si>
   <si>
-    <t>&lt;name of the github project&gt;</t>
+    <t>Gautam</t>
+  </si>
+  <si>
+    <t>Ramesh</t>
+  </si>
+  <si>
+    <t>gautam-GGEZ</t>
+  </si>
+  <si>
+    <t>gautam.ramesh.1@stud.emden-leer.de</t>
+  </si>
+  <si>
+    <t>gaudeep0901@gmail.com</t>
+  </si>
+  <si>
+    <t>Hochschule Emden/Leer</t>
+  </si>
+  <si>
+    <t>Graf-Enno-Straße 57</t>
+  </si>
+  <si>
+    <t>MBIDA</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering Department</t>
+  </si>
+  <si>
+    <t>26723 Emden</t>
+  </si>
+  <si>
+    <t>Project T</t>
+  </si>
+  <si>
+    <t>Licence plate detection using Jetson nano</t>
+  </si>
+  <si>
+    <t>ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano</t>
+  </si>
+  <si>
+    <t>A real-time system using the Jetson Nano to detect vehicles, locate license plates with computer vision models (e.g., YOLO), and apply OCR to read plate numbers. It runs entirely on-device, making it efficient for traffic monitoring and security applications.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +269,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -242,10 +295,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -260,9 +314,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -539,37 +595,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="63.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -583,557 +642,568 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7026787</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="1">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1">
+        <v>36534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="B22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="B23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33">
+        <v>15510820227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
       </c>
-      <c r="B50" t="s">
-        <v>25</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{7A14ECE8-547E-4548-A794-2DE01C65D89A}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{CB70E530-2C01-A94A-ADFD-BAD780E88518}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1142,277 +1212,277 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10921"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0290E8CF-22B3-1D4A-9C9E-F24696FD0B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C808C3-28FA-7D43-BCA9-BFE4E1AC27B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="25260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>Short Description</t>
   </si>
@@ -223,6 +223,42 @@
   </si>
   <si>
     <t>A real-time system using the Jetson Nano to detect vehicles, locate license plates with computer vision models (e.g., YOLO), and apply OCR to read plate numbers. It runs entirely on-device, making it efficient for traffic monitoring and security applications.</t>
+  </si>
+  <si>
+    <t>Siddhanth</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>ssid1998</t>
+  </si>
+  <si>
+    <t>siddhanth.sharma@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>ssid1998@gmail.com</t>
+  </si>
+  <si>
+    <t>Business Intelligen ans Data Analytics</t>
+  </si>
+  <si>
+    <t>02.01.1998</t>
+  </si>
+  <si>
+    <t>24.09.25</t>
+  </si>
+  <si>
+    <t>29.01.26</t>
+  </si>
+  <si>
+    <t>Klein-von-Diepold-Straße 10, Wohnungsnummer 98</t>
+  </si>
+  <si>
+    <t>26721 Emden</t>
+  </si>
+  <si>
+    <t>Masters in Business Intelligence and Data Analytics</t>
   </si>
 </sst>
 </file>
@@ -299,7 +335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -308,13 +344,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -603,11 +645,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -615,11 +657,11 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -691,10 +733,10 @@
       <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>53</v>
       </c>
     </row>
@@ -705,36 +747,48 @@
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>2</v>
       </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1">
-        <v>45924</v>
+      <c r="B12" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1">
-        <v>45594</v>
-      </c>
+      <c r="B13" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
     </row>
@@ -742,28 +796,38 @@
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>5</v>
       </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="9">
         <v>36534</v>
       </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -771,25 +835,28 @@
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>57</v>
       </c>
     </row>
@@ -797,7 +864,7 @@
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -805,20 +872,27 @@
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B31" s="2"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <v>15510820227</v>
       </c>
     </row>
@@ -826,25 +900,29 @@
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="B34" s="2"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
+      <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="B37" s="2"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -852,7 +930,7 @@
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -860,29 +938,33 @@
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
+      <c r="B41" s="2"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
+      <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
+      <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -890,7 +972,7 @@
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -898,7 +980,7 @@
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -917,7 +999,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
@@ -938,9 +1020,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -970,13 +1053,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
+        <v>7027189</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -986,96 +1078,124 @@
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1">
-        <v>45351</v>
+      <c r="B12" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1">
-        <v>45594</v>
-      </c>
+      <c r="B13" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="B15" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
-        <v>7</v>
+      <c r="B22" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
-        <v>11</v>
+      <c r="B25" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>12</v>
+      <c r="B26" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>35</v>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1083,52 +1203,57 @@
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
+      <c r="B29" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B31" s="2"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B32" s="10">
+        <v>15510941084</v>
+      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
+      <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
+      <c r="B34" s="2"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
+      <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
+      <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="B37" s="2"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1136,7 +1261,7 @@
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1144,29 +1269,33 @@
       <c r="A40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
+      <c r="B41" s="2"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
+      <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
+      <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1174,7 +1303,7 @@
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1182,7 +1311,7 @@
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1207,7 +1336,12 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{A9A95275-001F-5749-9E02-1A0F04F634C2}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{0EFD6D52-1573-F24A-8554-860F96E9AB07}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CF5DD5-A491-401F-930E-21D54EECFD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B31AB-98C7-594A-9BB6-CDC32538E85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="680" windowWidth="23260" windowHeight="12580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="65">
   <si>
     <t>Short Description</t>
   </si>
@@ -212,21 +212,6 @@
   </si>
   <si>
     <t>Masters in Business Intelligence and Data Analytics</t>
-  </si>
-  <si>
-    <t>Vedant</t>
-  </si>
-  <si>
-    <t>Purohit</t>
-  </si>
-  <si>
-    <t>Ved-Purohit22</t>
-  </si>
-  <si>
-    <t>vedant.ramkrishna.purohit@stud.hs-emden-leer.de</t>
-  </si>
-  <si>
-    <t>ved.purohit22@gmail.com</t>
   </si>
   <si>
     <t>22.12.1999</t>
@@ -612,36 +597,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -659,21 +644,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -693,7 +678,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -713,10 +698,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -724,10 +709,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -735,10 +720,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -746,7 +731,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -754,10 +739,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -765,7 +750,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -773,13 +758,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
@@ -787,16 +772,16 @@
         <v>36534</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -804,7 +789,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -812,10 +797,10 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -823,17 +808,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -841,7 +826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -849,19 +834,19 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -869,29 +854,29 @@
         <v>15510820227</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -899,7 +884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -907,7 +892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -915,25 +900,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -941,7 +926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -949,7 +934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -957,13 +942,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -990,21 +975,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1024,7 +1009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1044,10 +1029,10 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1055,10 +1040,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -1066,10 +1051,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1077,7 +1062,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1085,10 +1070,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1096,7 +1081,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1104,13 +1089,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
@@ -1118,16 +1103,16 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -1135,7 +1120,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1143,10 +1128,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1154,17 +1139,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -1172,7 +1157,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -1180,13 +1165,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -1194,35 +1179,35 @@
         <v>15510941084</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -1230,7 +1215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -1238,7 +1223,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -1246,25 +1231,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -1272,7 +1257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -1280,7 +1265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -1288,13 +1273,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -1321,21 +1306,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1355,30 +1340,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="1">
-        <v>7027292</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C5" s="1"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1386,7 +1355,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -1394,7 +1363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1402,7 +1371,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1410,7 +1379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1418,7 +1387,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1426,28 +1395,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1455,7 +1424,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1463,17 +1432,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1450,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -1489,35 +1458,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -1525,7 +1494,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -1533,7 +1502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -1541,21 +1510,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -1563,7 +1532,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -1571,7 +1540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -1579,13 +1548,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -1600,9 +1569,6 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{37BDC1F4-AC28-461A-83EA-E10A8AB698A1}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B31AB-98C7-594A-9BB6-CDC32538E85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E720B6-7D54-49B5-BBF1-E9D0AEADB2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="680" windowWidth="23260" windowHeight="12580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="71">
   <si>
     <t>Short Description</t>
   </si>
@@ -214,10 +214,28 @@
     <t>Masters in Business Intelligence and Data Analytics</t>
   </si>
   <si>
-    <t>22.12.1999</t>
-  </si>
-  <si>
-    <t>Klein-von-Diepold-Straße 16, Wohnungsnummer 58</t>
+    <t>Shubhankar</t>
+  </si>
+  <si>
+    <t>Dumka</t>
+  </si>
+  <si>
+    <t>shubhankardumka4993-cloud</t>
+  </si>
+  <si>
+    <t>shubhankar.dumka@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>shubhankardumka4993@gmail.com</t>
+  </si>
+  <si>
+    <t>20.08.1993</t>
+  </si>
+  <si>
+    <t>Boltentorstrasse 23</t>
+  </si>
+  <si>
+    <t>+4915213715965</t>
   </si>
 </sst>
 </file>
@@ -294,7 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -315,6 +333,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -597,36 +616,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -644,21 +663,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.1640625" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -678,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -698,10 +717,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -709,10 +728,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -720,10 +739,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -731,7 +750,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -739,10 +758,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -750,7 +769,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -758,13 +777,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
@@ -772,16 +791,16 @@
         <v>36534</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -789,7 +808,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -797,10 +816,10 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -808,17 +827,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -826,7 +845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -834,19 +853,19 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -854,29 +873,29 @@
         <v>15510820227</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -884,7 +903,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -892,7 +911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -900,25 +919,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -926,7 +945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -934,7 +953,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -942,13 +961,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -975,21 +994,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1009,7 +1028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1029,10 +1048,10 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1040,10 +1059,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -1051,10 +1070,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1062,7 +1081,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1070,10 +1089,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1081,7 +1100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1089,13 +1108,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
@@ -1103,16 +1122,16 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -1120,7 +1139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1128,10 +1147,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1139,17 +1158,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -1157,7 +1176,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -1165,13 +1184,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -1179,35 +1198,35 @@
         <v>15510941084</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -1215,7 +1234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -1223,7 +1242,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -1231,25 +1250,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -1257,7 +1276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -1265,7 +1284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -1273,13 +1292,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -1306,21 +1325,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1340,14 +1360,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C5" s="1"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7027187</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1355,7 +1391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -1363,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1371,7 +1407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1379,7 +1415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1387,7 +1423,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1395,28 +1431,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1424,7 +1460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1432,17 +1468,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -1450,7 +1486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -1458,35 +1494,38 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B32" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -1494,7 +1533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -1502,7 +1541,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -1510,21 +1549,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
@@ -1532,7 +1571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -1540,7 +1579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -1548,13 +1587,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -1570,5 +1609,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>